--- a/input/Domains/Game/SkillTable.xlsx
+++ b/input/Domains/Game/SkillTable.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4940" yWindow="1800" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SKILL" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PROJECTILE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="STATUS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AFFECT" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKILL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROJECTILE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STATUS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AFFECT" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -496,19 +496,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="49.5" customFormat="1" customHeight="1" s="2">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>skillId</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>nameId</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>affectList</t>
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>skill_id</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>name_id</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>affect_list</t>
         </is>
       </c>
     </row>
@@ -544,12 +544,12 @@
           <t>스킬 ID (정본)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>이름 텍스트 ID</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>AFFECT ID 목록</t>
         </is>
@@ -588,19 +588,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="49.5" customFormat="1" customHeight="1" s="2">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>projectileId</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>nameId</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>affectList</t>
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>projectile_id</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>name_id</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>affect_list</t>
         </is>
       </c>
     </row>
@@ -636,12 +636,12 @@
           <t>투사체 ID (정본)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>이름 텍스트 ID</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>AFFECT ID 목록</t>
         </is>
@@ -662,19 +662,19 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <sheetData>
     <row r="1" ht="49.5" customFormat="1" customHeight="1" s="2">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>statusId</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>nameId</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>affectList</t>
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>status_id</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>name_id</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>affect_list</t>
         </is>
       </c>
     </row>
@@ -710,12 +710,12 @@
           <t>상태 ID (정본)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>이름 텍스트 ID</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>AFFECT ID 목록</t>
         </is>
@@ -740,14 +740,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="49.5" customFormat="1" customHeight="1" s="2">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>affectId</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>nameId</t>
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>affect_id</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>name_id</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
           <t>효과 ID (정본)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>이름 텍스트 ID</t>
         </is>

--- a/input/Domains/Game/SkillTable.xlsx
+++ b/input/Domains/Game/SkillTable.xlsx
@@ -1,52 +1,113 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Game/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4AE018-3DA0-1047-8BA6-31E88CD0D2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4940" yWindow="1800" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="1240" yWindow="500" windowWidth="37160" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKILL" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROJECTILE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STATUS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AFFECT" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="SKILL" sheetId="1" r:id="rId1"/>
+    <sheet name="PROJECTILE" sheetId="2" r:id="rId2"/>
+    <sheet name="STATUS" sheetId="3" r:id="rId3"/>
+    <sheet name="AFFECT" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="17">
+  <si>
+    <t>skill_id</t>
+  </si>
+  <si>
+    <t>name_id</t>
+  </si>
+  <si>
+    <t>affect_list</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>string[]</t>
+  </si>
+  <si>
+    <t>pk</t>
+  </si>
+  <si>
+    <t>스킬 ID (정본)</t>
+  </si>
+  <si>
+    <t>이름 텍스트 ID</t>
+  </si>
+  <si>
+    <t>AFFECT ID 목록</t>
+  </si>
+  <si>
+    <t>ATTACK</t>
+  </si>
+  <si>
+    <t>STUN</t>
+  </si>
+  <si>
+    <t>projectile_id</t>
+  </si>
+  <si>
+    <t>투사체 ID (정본)</t>
+  </si>
+  <si>
+    <t>status_id</t>
+  </si>
+  <si>
+    <t>상태 ID (정본)</t>
+  </si>
+  <si>
+    <t>affect_id</t>
+  </si>
+  <si>
+    <t>효과 ID (정본)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -58,7 +119,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7999816888943144"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -88,102 +149,46 @@
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
+    <cellStyle name="20% - 강조색5" xfId="2" builtinId="46"/>
+    <cellStyle name="메모" xfId="1" builtinId="10"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="메모" xfId="1" builtinId="10"/>
-    <cellStyle name="20% - 강조색5" xfId="2" builtinId="46"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -483,307 +488,210 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="17.6640625" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.83203125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col min="1" max="1" width="17.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="49.5" customFormat="1" customHeight="1" s="2">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>skill_id</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>name_id</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>affect_list</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" customFormat="1" s="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>string[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>pk</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n"/>
-      <c r="C3" s="1" t="n"/>
-    </row>
-    <row r="4" customFormat="1" s="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>스킬 ID (정본)</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>이름 텍스트 ID</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>AFFECT ID 목록</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>ATTACK</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>STUN</t>
-        </is>
+    <row r="1" spans="1:3" s="2" customFormat="1" ht="49.5" customHeight="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="1" customFormat="1">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="1" customFormat="1">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="4" customFormat="1">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="17.6640625" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.83203125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col min="1" max="1" width="17.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="49.5" customFormat="1" customHeight="1" s="2">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>projectile_id</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>name_id</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>affect_list</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" customFormat="1" s="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>string[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>pk</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n"/>
-      <c r="C3" s="1" t="n"/>
-    </row>
-    <row r="4" customFormat="1" s="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>투사체 ID (정본)</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>이름 텍스트 ID</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>AFFECT ID 목록</t>
-        </is>
+    <row r="1" spans="1:3" s="2" customFormat="1" ht="49.5" customHeight="1">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="1" customFormat="1">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="1" customFormat="1">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="4" customFormat="1">
+      <c r="A4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <sheetData>
-    <row r="1" ht="49.5" customFormat="1" customHeight="1" s="2">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>status_id</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>name_id</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>affect_list</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" customFormat="1" s="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>string[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>pk</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n"/>
-      <c r="C3" s="1" t="n"/>
-    </row>
-    <row r="4" customFormat="1" s="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>상태 ID (정본)</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>이름 텍스트 ID</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>AFFECT ID 목록</t>
-        </is>
+    <row r="1" spans="1:3" s="2" customFormat="1" ht="49.5" customHeight="1">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="1" customFormat="1">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="1" customFormat="1">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="4" customFormat="1">
+      <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="17.6640625" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.83203125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col min="1" max="1" width="17.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="49.5" customFormat="1" customHeight="1" s="2">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>affect_id</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>name_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" customFormat="1" s="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>pk</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n"/>
-    </row>
-    <row r="4" customFormat="1" s="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>효과 ID (정본)</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>이름 텍스트 ID</t>
-        </is>
+    <row r="1" spans="1:2" s="2" customFormat="1" ht="49.5" customHeight="1">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="4" customFormat="1">
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="4" customFormat="1">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="4" customFormat="1">
+      <c r="A4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>